--- a/Empreendimentos.xlsx
+++ b/Empreendimentos.xlsx
@@ -1,18 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/Formulario/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_848C2FC8A4B27389F3B341269182C3234C539139" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F907D9C2-6064-4EEA-A7DB-633DD499AC77}"/>
+  <bookViews>
+    <workbookView xWindow="28680" yWindow="-4950" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId5"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$2:$E$108</definedName>
+  </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="365">
   <si>
     <t>EMPREENDIMENTO</t>
   </si>
@@ -632,7 +643,7 @@
     <t>AVENIDA VISCONDE DE ALBUQUERQUE, 29/701</t>
   </si>
   <si>
-    <t xml:space="preserve">2304 -  LEONARDO ALMEIDA BYRRO</t>
+    <t>2304 -  LEONARDO ALMEIDA BYRRO</t>
   </si>
   <si>
     <t>26927536825</t>
@@ -767,7 +778,7 @@
     <t>22630011</t>
   </si>
   <si>
-    <t xml:space="preserve">AVENIDA LÚCIO COSTA, 4260, BLOCO 3 -  AP</t>
+    <t>AVENIDA LÚCIO COSTA, 4260, BLOCO 3 -  AP</t>
   </si>
   <si>
     <t>2317 - LUIZ ALBERTO HESS BORGES</t>
@@ -809,7 +820,7 @@
     <t>01049911</t>
   </si>
   <si>
-    <t xml:space="preserve">RUA FORMOSA, 367 -  ANDAR 15</t>
+    <t>RUA FORMOSA, 367 -  ANDAR 15</t>
   </si>
   <si>
     <t>2404 - LUIZ HENRIQUE FRAGA</t>
@@ -1062,6 +1073,18 @@
   </si>
   <si>
     <t xml:space="preserve"> 04351672862</t>
+  </si>
+  <si>
+    <t>2601 - REGINA CAMPOS SALLES MORAES ABREU</t>
+  </si>
+  <si>
+    <t>04383430856</t>
+  </si>
+  <si>
+    <t>01456010</t>
+  </si>
+  <si>
+    <t>RUA CAMPO VERDE, 262 - CASA 04</t>
   </si>
   <si>
     <t>9991 - DÉBITO ADMINISTRAÇÃO (OBRAS)</t>
@@ -1100,14 +1123,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="28"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -1123,38 +1141,42 @@
   </fills>
   <borders count="1">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Larissa-Design">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Larissa">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1192,19 +1214,79 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Larissa">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Larissa">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1377,22 +1459,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:E107"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E108"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.7142857142857" customWidth="1" style="1"/>
-    <col min="2" max="2" width="15" customWidth="1" style="1"/>
-    <col min="3" max="3" width="9" customWidth="1" style="1"/>
-    <col min="4" max="4" width="46.4285714285714" customWidth="1" style="1"/>
-    <col min="5" max="5" width="3.57142857142857" customWidth="1" style="1"/>
-    <col min="6" max="16384" width="11.4285714285714" style="1"/>
+    <col min="1" max="1" width="57.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1" customWidth="1"/>
+    <col min="4" max="4" width="46.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="3.5546875" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row ht="12.75" customHeight="1" r="1">
+    <row r="1" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1409,7 +1488,7 @@
         <v>4</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="2">
+    <row r="2" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1426,7 +1505,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="3">
+    <row r="3" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1443,7 +1522,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="4">
+    <row r="4" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1460,7 +1539,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="5">
+    <row r="5" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
@@ -1477,7 +1556,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="6">
+    <row r="6" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>23</v>
       </c>
@@ -1494,7 +1573,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="7">
+    <row r="7" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
@@ -1511,7 +1590,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="8">
+    <row r="8" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>30</v>
       </c>
@@ -1528,7 +1607,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="9">
+    <row r="9" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>34</v>
       </c>
@@ -1545,7 +1624,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="10">
+    <row r="10" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>37</v>
       </c>
@@ -1562,7 +1641,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="11">
+    <row r="11" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>41</v>
       </c>
@@ -1579,7 +1658,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="12">
+    <row r="12" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>45</v>
       </c>
@@ -1596,7 +1675,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="13">
+    <row r="13" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>49</v>
       </c>
@@ -1613,7 +1692,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="14">
+    <row r="14" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>53</v>
       </c>
@@ -1630,7 +1709,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="15">
+    <row r="15" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>57</v>
       </c>
@@ -1647,7 +1726,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="16">
+    <row r="16" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>61</v>
       </c>
@@ -1664,7 +1743,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="17">
+    <row r="17" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>65</v>
       </c>
@@ -1681,7 +1760,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="18">
+    <row r="18" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>69</v>
       </c>
@@ -1698,7 +1777,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="19">
+    <row r="19" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>72</v>
       </c>
@@ -1715,7 +1794,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="20">
+    <row r="20" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>74</v>
       </c>
@@ -1732,7 +1811,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="21">
+    <row r="21" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>77</v>
       </c>
@@ -1749,7 +1828,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="22">
+    <row r="22" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>81</v>
       </c>
@@ -1766,7 +1845,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="23">
+    <row r="23" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>85</v>
       </c>
@@ -1783,7 +1862,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="24">
+    <row r="24" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>89</v>
       </c>
@@ -1800,7 +1879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="25">
+    <row r="25" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>92</v>
       </c>
@@ -1817,7 +1896,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="26">
+    <row r="26" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>95</v>
       </c>
@@ -1834,7 +1913,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="27">
+    <row r="27" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>99</v>
       </c>
@@ -1851,7 +1930,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="28">
+    <row r="28" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>101</v>
       </c>
@@ -1868,7 +1947,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="29">
+    <row r="29" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>104</v>
       </c>
@@ -1885,7 +1964,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="30">
+    <row r="30" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>108</v>
       </c>
@@ -1902,7 +1981,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="31">
+    <row r="31" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>111</v>
       </c>
@@ -1919,7 +1998,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="32">
+    <row r="32" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>115</v>
       </c>
@@ -1936,7 +2015,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="33">
+    <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>117</v>
       </c>
@@ -1953,7 +2032,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="34">
+    <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>121</v>
       </c>
@@ -1970,7 +2049,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="35">
+    <row r="35" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>123</v>
       </c>
@@ -1987,7 +2066,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="36">
+    <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>127</v>
       </c>
@@ -2004,7 +2083,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="37">
+    <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>129</v>
       </c>
@@ -2021,7 +2100,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="38">
+    <row r="38" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>132</v>
       </c>
@@ -2038,7 +2117,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="39">
+    <row r="39" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>134</v>
       </c>
@@ -2055,7 +2134,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="40">
+    <row r="40" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>138</v>
       </c>
@@ -2072,7 +2151,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="41">
+    <row r="41" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>142</v>
       </c>
@@ -2089,7 +2168,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="42">
+    <row r="42" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>146</v>
       </c>
@@ -2106,7 +2185,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="43">
+    <row r="43" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>148</v>
       </c>
@@ -2123,7 +2202,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="44">
+    <row r="44" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>152</v>
       </c>
@@ -2140,7 +2219,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="45">
+    <row r="45" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>156</v>
       </c>
@@ -2157,7 +2236,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="46">
+    <row r="46" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>158</v>
       </c>
@@ -2174,7 +2253,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="47">
+    <row r="47" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>162</v>
       </c>
@@ -2191,7 +2270,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="48">
+    <row r="48" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>165</v>
       </c>
@@ -2208,7 +2287,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="49">
+    <row r="49" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>169</v>
       </c>
@@ -2225,7 +2304,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="50">
+    <row r="50" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>171</v>
       </c>
@@ -2242,7 +2321,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="51">
+    <row r="51" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>175</v>
       </c>
@@ -2259,7 +2338,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="52">
+    <row r="52" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>179</v>
       </c>
@@ -2276,7 +2355,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="53">
+    <row r="53" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>181</v>
       </c>
@@ -2293,7 +2372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="54">
+    <row r="54" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>185</v>
       </c>
@@ -2310,7 +2389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="55">
+    <row r="55" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>187</v>
       </c>
@@ -2327,7 +2406,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="56">
+    <row r="56" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>191</v>
       </c>
@@ -2344,7 +2423,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="57">
+    <row r="57" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>194</v>
       </c>
@@ -2361,7 +2440,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="58">
+    <row r="58" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>198</v>
       </c>
@@ -2378,7 +2457,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="59">
+    <row r="59" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>202</v>
       </c>
@@ -2395,7 +2474,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="60">
+    <row r="60" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>206</v>
       </c>
@@ -2412,7 +2491,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="61">
+    <row r="61" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>210</v>
       </c>
@@ -2429,7 +2508,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="62">
+    <row r="62" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>213</v>
       </c>
@@ -2446,7 +2525,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="63">
+    <row r="63" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>216</v>
       </c>
@@ -2463,7 +2542,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="64">
+    <row r="64" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>219</v>
       </c>
@@ -2480,7 +2559,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="65">
+    <row r="65" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>223</v>
       </c>
@@ -2497,7 +2576,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="66">
+    <row r="66" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>227</v>
       </c>
@@ -2514,7 +2593,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="67">
+    <row r="67" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>231</v>
       </c>
@@ -2531,7 +2610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="68">
+    <row r="68" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>234</v>
       </c>
@@ -2548,7 +2627,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="69">
+    <row r="69" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>238</v>
       </c>
@@ -2565,7 +2644,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="70">
+    <row r="70" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>241</v>
       </c>
@@ -2582,7 +2661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="71">
+    <row r="71" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>245</v>
       </c>
@@ -2599,7 +2678,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="72">
+    <row r="72" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>248</v>
       </c>
@@ -2616,7 +2695,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="73">
+    <row r="73" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>252</v>
       </c>
@@ -2633,7 +2712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="74">
+    <row r="74" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>256</v>
       </c>
@@ -2650,7 +2729,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="75">
+    <row r="75" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>260</v>
       </c>
@@ -2667,7 +2746,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="76">
+    <row r="76" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>263</v>
       </c>
@@ -2684,7 +2763,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="77">
+    <row r="77" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>266</v>
       </c>
@@ -2701,7 +2780,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="78">
+    <row r="78" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>269</v>
       </c>
@@ -2718,7 +2797,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="79">
+    <row r="79" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>273</v>
       </c>
@@ -2735,7 +2814,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="80">
+    <row r="80" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>277</v>
       </c>
@@ -2752,7 +2831,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="81">
+    <row r="81" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>280</v>
       </c>
@@ -2769,7 +2848,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="82">
+    <row r="82" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>283</v>
       </c>
@@ -2786,7 +2865,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="83">
+    <row r="83" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>287</v>
       </c>
@@ -2803,7 +2882,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="84">
+    <row r="84" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>291</v>
       </c>
@@ -2820,7 +2899,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="85">
+    <row r="85" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>293</v>
       </c>
@@ -2837,7 +2916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="86">
+    <row r="86" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>297</v>
       </c>
@@ -2854,7 +2933,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="87">
+    <row r="87" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>301</v>
       </c>
@@ -2871,7 +2950,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="88">
+    <row r="88" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>304</v>
       </c>
@@ -2888,7 +2967,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="89">
+    <row r="89" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>306</v>
       </c>
@@ -2905,7 +2984,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="90">
+    <row r="90" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>309</v>
       </c>
@@ -2922,7 +3001,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="91">
+    <row r="91" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>312</v>
       </c>
@@ -2939,7 +3018,7 @@
         <v>316</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="92">
+    <row r="92" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>317</v>
       </c>
@@ -2956,7 +3035,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="93">
+    <row r="93" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>320</v>
       </c>
@@ -2973,7 +3052,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="94">
+    <row r="94" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>322</v>
       </c>
@@ -2990,7 +3069,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="95">
+    <row r="95" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>325</v>
       </c>
@@ -3007,7 +3086,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="96">
+    <row r="96" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>328</v>
       </c>
@@ -3024,7 +3103,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="97">
+    <row r="97" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>331</v>
       </c>
@@ -3041,7 +3120,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="98">
+    <row r="98" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>335</v>
       </c>
@@ -3058,7 +3137,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="99">
+    <row r="99" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>338</v>
       </c>
@@ -3075,7 +3154,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="100">
+    <row r="100" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>341</v>
       </c>
@@ -3092,7 +3171,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="101">
+    <row r="101" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>345</v>
       </c>
@@ -3109,7 +3188,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="102">
+    <row r="102" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>348</v>
       </c>
@@ -3126,7 +3205,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="103">
+    <row r="103" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>350</v>
       </c>
@@ -3140,79 +3219,96 @@
         <v>353</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="104">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>354</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="105">
+    <row r="105" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="C105" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>357</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="106">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B106" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="C107" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D106" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="107">
-      <c r="A107" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="B107" s="1" t="s">
+      <c r="D107" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C108" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D107" s="1" t="s">
+      <c r="D108" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="E107" s="1" t="s">
+      <c r="E108" s="1" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>
-  <pageSetup orientation="portrait" pageOrder="downThenOver" paperSize="9" fitToWidth="0" fitToHeight="0"/>
+  <pageMargins left="0.78740157480314998" right="0.78740157480314998" top="0.78740157480314998" bottom="0.78740157480314998" header="0.39370078740157499" footer="0.39370078740157499"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Empreendimentos.xlsx
+++ b/Empreendimentos.xlsx
@@ -1,29 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/Formulario/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_848C2FC8A4B27389F3B341269182C3234C539139" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F907D9C2-6064-4EEA-A7DB-633DD499AC77}"/>
-  <bookViews>
-    <workbookView xWindow="28680" yWindow="-4950" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId5"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$2:$E$108</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="369">
   <si>
     <t>EMPREENDIMENTO</t>
   </si>
@@ -643,7 +632,7 @@
     <t>AVENIDA VISCONDE DE ALBUQUERQUE, 29/701</t>
   </si>
   <si>
-    <t>2304 -  LEONARDO ALMEIDA BYRRO</t>
+    <t xml:space="preserve">2304 -  LEONARDO ALMEIDA BYRRO</t>
   </si>
   <si>
     <t>26927536825</t>
@@ -778,7 +767,7 @@
     <t>22630011</t>
   </si>
   <si>
-    <t>AVENIDA LÚCIO COSTA, 4260, BLOCO 3 -  AP</t>
+    <t xml:space="preserve">AVENIDA LÚCIO COSTA, 4260, BLOCO 3 -  AP</t>
   </si>
   <si>
     <t>2317 - LUIZ ALBERTO HESS BORGES</t>
@@ -820,7 +809,7 @@
     <t>01049911</t>
   </si>
   <si>
-    <t>RUA FORMOSA, 367 -  ANDAR 15</t>
+    <t xml:space="preserve">RUA FORMOSA, 367 -  ANDAR 15</t>
   </si>
   <si>
     <t>2404 - LUIZ HENRIQUE FRAGA</t>
@@ -1085,6 +1074,18 @@
   </si>
   <si>
     <t>RUA CAMPO VERDE, 262 - CASA 04</t>
+  </si>
+  <si>
+    <t>2602 - RENATA STUHLBERGER</t>
+  </si>
+  <si>
+    <t>22761084870</t>
+  </si>
+  <si>
+    <t>01423010</t>
+  </si>
+  <si>
+    <t>RUA BATATAES 586, APT 91</t>
   </si>
   <si>
     <t>9991 - DÉBITO ADMINISTRAÇÃO (OBRAS)</t>
@@ -1123,9 +1124,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="28"/>
+  <fonts count="1">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -1141,42 +1147,38 @@
   </fills>
   <borders count="1">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Larissa-Design">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Larissa">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1214,79 +1216,19 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Larissa">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Larissa">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1459,19 +1401,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E108"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:E109"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="57.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="1" customWidth="1"/>
-    <col min="4" max="4" width="46.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="3.5546875" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="11.44140625" style="1"/>
+    <col min="1" max="1" width="57.7142857142857" customWidth="1" style="1"/>
+    <col min="2" max="2" width="15" customWidth="1" style="1"/>
+    <col min="3" max="3" width="9" customWidth="1" style="1"/>
+    <col min="4" max="4" width="46.4285714285714" customWidth="1" style="1"/>
+    <col min="5" max="5" width="3.57142857142857" customWidth="1" style="1"/>
+    <col min="6" max="16384" width="11.4285714285714" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1488,7 +1433,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1505,7 +1450,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="3">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1522,7 +1467,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="4">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1539,7 +1484,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="5">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
@@ -1556,7 +1501,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="6">
       <c r="A6" s="1" t="s">
         <v>23</v>
       </c>
@@ -1573,7 +1518,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="7">
       <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
@@ -1590,7 +1535,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="8">
       <c r="A8" s="1" t="s">
         <v>30</v>
       </c>
@@ -1607,7 +1552,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="9">
       <c r="A9" s="1" t="s">
         <v>34</v>
       </c>
@@ -1624,7 +1569,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="10">
       <c r="A10" s="1" t="s">
         <v>37</v>
       </c>
@@ -1641,7 +1586,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="11">
       <c r="A11" s="1" t="s">
         <v>41</v>
       </c>
@@ -1658,7 +1603,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="12">
       <c r="A12" s="1" t="s">
         <v>45</v>
       </c>
@@ -1675,7 +1620,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="13">
       <c r="A13" s="1" t="s">
         <v>49</v>
       </c>
@@ -1692,7 +1637,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="14">
       <c r="A14" s="1" t="s">
         <v>53</v>
       </c>
@@ -1709,7 +1654,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="15">
       <c r="A15" s="1" t="s">
         <v>57</v>
       </c>
@@ -1726,7 +1671,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="16">
       <c r="A16" s="1" t="s">
         <v>61</v>
       </c>
@@ -1743,7 +1688,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="17">
       <c r="A17" s="1" t="s">
         <v>65</v>
       </c>
@@ -1760,7 +1705,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="18">
       <c r="A18" s="1" t="s">
         <v>69</v>
       </c>
@@ -1777,7 +1722,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="19">
       <c r="A19" s="1" t="s">
         <v>72</v>
       </c>
@@ -1794,7 +1739,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="20">
       <c r="A20" s="1" t="s">
         <v>74</v>
       </c>
@@ -1811,7 +1756,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="21">
       <c r="A21" s="1" t="s">
         <v>77</v>
       </c>
@@ -1828,7 +1773,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="22">
       <c r="A22" s="1" t="s">
         <v>81</v>
       </c>
@@ -1845,7 +1790,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="23">
       <c r="A23" s="1" t="s">
         <v>85</v>
       </c>
@@ -1862,7 +1807,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="24">
       <c r="A24" s="1" t="s">
         <v>89</v>
       </c>
@@ -1879,7 +1824,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="25">
       <c r="A25" s="1" t="s">
         <v>92</v>
       </c>
@@ -1896,7 +1841,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="26">
       <c r="A26" s="1" t="s">
         <v>95</v>
       </c>
@@ -1913,7 +1858,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="27">
       <c r="A27" s="1" t="s">
         <v>99</v>
       </c>
@@ -1930,7 +1875,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="28">
       <c r="A28" s="1" t="s">
         <v>101</v>
       </c>
@@ -1947,7 +1892,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="29">
       <c r="A29" s="1" t="s">
         <v>104</v>
       </c>
@@ -1964,7 +1909,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="30">
       <c r="A30" s="1" t="s">
         <v>108</v>
       </c>
@@ -1981,7 +1926,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="31">
       <c r="A31" s="1" t="s">
         <v>111</v>
       </c>
@@ -1998,7 +1943,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="32">
       <c r="A32" s="1" t="s">
         <v>115</v>
       </c>
@@ -2015,7 +1960,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="33">
       <c r="A33" s="1" t="s">
         <v>117</v>
       </c>
@@ -2032,7 +1977,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="34">
       <c r="A34" s="1" t="s">
         <v>121</v>
       </c>
@@ -2049,7 +1994,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="35">
       <c r="A35" s="1" t="s">
         <v>123</v>
       </c>
@@ -2066,7 +2011,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="36">
       <c r="A36" s="1" t="s">
         <v>127</v>
       </c>
@@ -2083,7 +2028,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="37">
       <c r="A37" s="1" t="s">
         <v>129</v>
       </c>
@@ -2100,7 +2045,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="38">
       <c r="A38" s="1" t="s">
         <v>132</v>
       </c>
@@ -2117,7 +2062,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="39">
       <c r="A39" s="1" t="s">
         <v>134</v>
       </c>
@@ -2134,7 +2079,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="40">
       <c r="A40" s="1" t="s">
         <v>138</v>
       </c>
@@ -2151,7 +2096,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="41">
       <c r="A41" s="1" t="s">
         <v>142</v>
       </c>
@@ -2168,7 +2113,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="42">
       <c r="A42" s="1" t="s">
         <v>146</v>
       </c>
@@ -2185,7 +2130,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="43">
       <c r="A43" s="1" t="s">
         <v>148</v>
       </c>
@@ -2202,7 +2147,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="44">
       <c r="A44" s="1" t="s">
         <v>152</v>
       </c>
@@ -2219,7 +2164,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="45">
       <c r="A45" s="1" t="s">
         <v>156</v>
       </c>
@@ -2236,7 +2181,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="46">
       <c r="A46" s="1" t="s">
         <v>158</v>
       </c>
@@ -2253,7 +2198,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="47">
       <c r="A47" s="1" t="s">
         <v>162</v>
       </c>
@@ -2270,7 +2215,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="48">
       <c r="A48" s="1" t="s">
         <v>165</v>
       </c>
@@ -2287,7 +2232,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="49">
       <c r="A49" s="1" t="s">
         <v>169</v>
       </c>
@@ -2304,7 +2249,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="50">
       <c r="A50" s="1" t="s">
         <v>171</v>
       </c>
@@ -2321,7 +2266,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="51">
       <c r="A51" s="1" t="s">
         <v>175</v>
       </c>
@@ -2338,7 +2283,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="52">
       <c r="A52" s="1" t="s">
         <v>179</v>
       </c>
@@ -2355,7 +2300,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="53">
       <c r="A53" s="1" t="s">
         <v>181</v>
       </c>
@@ -2372,7 +2317,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="54">
       <c r="A54" s="1" t="s">
         <v>185</v>
       </c>
@@ -2389,7 +2334,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="55">
       <c r="A55" s="1" t="s">
         <v>187</v>
       </c>
@@ -2406,7 +2351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="56">
       <c r="A56" s="1" t="s">
         <v>191</v>
       </c>
@@ -2423,7 +2368,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="57">
       <c r="A57" s="1" t="s">
         <v>194</v>
       </c>
@@ -2440,7 +2385,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="58">
       <c r="A58" s="1" t="s">
         <v>198</v>
       </c>
@@ -2457,7 +2402,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="59">
       <c r="A59" s="1" t="s">
         <v>202</v>
       </c>
@@ -2474,7 +2419,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="60">
       <c r="A60" s="1" t="s">
         <v>206</v>
       </c>
@@ -2491,7 +2436,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="61">
       <c r="A61" s="1" t="s">
         <v>210</v>
       </c>
@@ -2508,7 +2453,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="62">
       <c r="A62" s="1" t="s">
         <v>213</v>
       </c>
@@ -2525,7 +2470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="63">
       <c r="A63" s="1" t="s">
         <v>216</v>
       </c>
@@ -2542,7 +2487,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="64">
       <c r="A64" s="1" t="s">
         <v>219</v>
       </c>
@@ -2559,7 +2504,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="65">
       <c r="A65" s="1" t="s">
         <v>223</v>
       </c>
@@ -2576,7 +2521,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="66">
       <c r="A66" s="1" t="s">
         <v>227</v>
       </c>
@@ -2593,7 +2538,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="67">
       <c r="A67" s="1" t="s">
         <v>231</v>
       </c>
@@ -2610,7 +2555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="68">
       <c r="A68" s="1" t="s">
         <v>234</v>
       </c>
@@ -2627,7 +2572,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="69">
       <c r="A69" s="1" t="s">
         <v>238</v>
       </c>
@@ -2644,7 +2589,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="70">
       <c r="A70" s="1" t="s">
         <v>241</v>
       </c>
@@ -2661,7 +2606,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="71">
       <c r="A71" s="1" t="s">
         <v>245</v>
       </c>
@@ -2678,7 +2623,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="72">
       <c r="A72" s="1" t="s">
         <v>248</v>
       </c>
@@ -2695,7 +2640,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="73">
       <c r="A73" s="1" t="s">
         <v>252</v>
       </c>
@@ -2712,7 +2657,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="74">
       <c r="A74" s="1" t="s">
         <v>256</v>
       </c>
@@ -2729,7 +2674,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="75">
       <c r="A75" s="1" t="s">
         <v>260</v>
       </c>
@@ -2746,7 +2691,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="76">
       <c r="A76" s="1" t="s">
         <v>263</v>
       </c>
@@ -2763,7 +2708,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="77">
       <c r="A77" s="1" t="s">
         <v>266</v>
       </c>
@@ -2780,7 +2725,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="78">
       <c r="A78" s="1" t="s">
         <v>269</v>
       </c>
@@ -2797,7 +2742,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="79">
       <c r="A79" s="1" t="s">
         <v>273</v>
       </c>
@@ -2814,7 +2759,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="80">
       <c r="A80" s="1" t="s">
         <v>277</v>
       </c>
@@ -2831,7 +2776,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="81">
       <c r="A81" s="1" t="s">
         <v>280</v>
       </c>
@@ -2848,7 +2793,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="82">
       <c r="A82" s="1" t="s">
         <v>283</v>
       </c>
@@ -2865,7 +2810,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="83">
       <c r="A83" s="1" t="s">
         <v>287</v>
       </c>
@@ -2882,7 +2827,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="84">
       <c r="A84" s="1" t="s">
         <v>291</v>
       </c>
@@ -2899,7 +2844,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="85">
       <c r="A85" s="1" t="s">
         <v>293</v>
       </c>
@@ -2916,7 +2861,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="86">
       <c r="A86" s="1" t="s">
         <v>297</v>
       </c>
@@ -2933,7 +2878,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="87">
       <c r="A87" s="1" t="s">
         <v>301</v>
       </c>
@@ -2950,7 +2895,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="88">
       <c r="A88" s="1" t="s">
         <v>304</v>
       </c>
@@ -2967,7 +2912,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="89">
       <c r="A89" s="1" t="s">
         <v>306</v>
       </c>
@@ -2984,7 +2929,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="90">
       <c r="A90" s="1" t="s">
         <v>309</v>
       </c>
@@ -3001,7 +2946,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="91">
       <c r="A91" s="1" t="s">
         <v>312</v>
       </c>
@@ -3018,7 +2963,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="92">
       <c r="A92" s="1" t="s">
         <v>317</v>
       </c>
@@ -3035,7 +2980,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="93">
       <c r="A93" s="1" t="s">
         <v>320</v>
       </c>
@@ -3052,7 +2997,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="94">
       <c r="A94" s="1" t="s">
         <v>322</v>
       </c>
@@ -3069,7 +3014,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="95">
       <c r="A95" s="1" t="s">
         <v>325</v>
       </c>
@@ -3086,7 +3031,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="96">
       <c r="A96" s="1" t="s">
         <v>328</v>
       </c>
@@ -3103,7 +3048,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="97">
       <c r="A97" s="1" t="s">
         <v>331</v>
       </c>
@@ -3120,7 +3065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="98">
       <c r="A98" s="1" t="s">
         <v>335</v>
       </c>
@@ -3137,7 +3082,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="99">
       <c r="A99" s="1" t="s">
         <v>338</v>
       </c>
@@ -3154,7 +3099,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="100">
       <c r="A100" s="1" t="s">
         <v>341</v>
       </c>
@@ -3171,7 +3116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="101">
       <c r="A101" s="1" t="s">
         <v>345</v>
       </c>
@@ -3188,7 +3133,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="102">
       <c r="A102" s="1" t="s">
         <v>348</v>
       </c>
@@ -3205,7 +3150,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="103">
       <c r="A103" s="1" t="s">
         <v>350</v>
       </c>
@@ -3222,7 +3167,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="104">
       <c r="A104" s="1" t="s">
         <v>354</v>
       </c>
@@ -3236,79 +3181,96 @@
         <v>357</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="105">
       <c r="A105" s="1" t="s">
         <v>358</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="106">
       <c r="A106" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="C106" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>361</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="107">
       <c r="A107" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B107" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="108">
+      <c r="A108" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C108" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D107" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="B108" s="1" t="s">
+      <c r="D108" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="109">
+      <c r="A109" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C109" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D108" s="1" t="s">
+      <c r="D109" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="E108" s="1" t="s">
+      <c r="E109" s="1" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.78740157480314998" right="0.78740157480314998" top="0.78740157480314998" bottom="0.78740157480314998" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
+  <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>
+  <pageSetup orientation="portrait" pageOrder="downThenOver" paperSize="9" fitToWidth="0" fitToHeight="0"/>
 </worksheet>
 </file>
--- a/Empreendimentos.xlsx
+++ b/Empreendimentos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="378">
   <si>
     <t>EMPREENDIMENTO</t>
   </si>
@@ -1088,6 +1088,24 @@
     <t>RUA BATATAES 586, APT 91</t>
   </si>
   <si>
+    <t>2603 - FERNANDO AUGUSTO COELHO F DE VASCONCELLOS</t>
+  </si>
+  <si>
+    <t>22420041</t>
+  </si>
+  <si>
+    <t>RUA PRUDENTE DE MORAIS, 1117</t>
+  </si>
+  <si>
+    <t>2604 - ANDRE FRANCO SALES</t>
+  </si>
+  <si>
+    <t>27799045850</t>
+  </si>
+  <si>
+    <t>RD SUMARÉ MONTE MOR KM09 - HARAS LARISSA</t>
+  </si>
+  <si>
     <t>9991 - DÉBITO ADMINISTRAÇÃO (OBRAS)</t>
   </si>
   <si>
@@ -1119,6 +1137,15 @@
   </si>
   <si>
     <t>240401 - LUIZ HENRIQUE FRAGA (PÓS-OBRA)</t>
+  </si>
+  <si>
+    <t>251001 - LUIZ ANTONIO BETTIOL</t>
+  </si>
+  <si>
+    <t>27981940168</t>
+  </si>
+  <si>
+    <t>AVENIDA VIEIRA SOUTO, 250</t>
   </si>
 </sst>
 </file>
@@ -1405,7 +1432,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="57.7142857142857" customWidth="1" style="1"/>
@@ -3189,13 +3216,13 @@
         <v>358</v>
       </c>
       <c r="B105" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="D105" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>361</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>14</v>
@@ -3203,47 +3230,47 @@
     </row>
     <row ht="12.75" customHeight="1" r="106">
       <c r="A106" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>359</v>
-      </c>
       <c r="C106" s="1" t="s">
-        <v>360</v>
+        <v>196</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="107">
       <c r="A107" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>79</v>
+        <v>366</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="108">
       <c r="A108" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>250</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>367</v>
@@ -3254,18 +3281,69 @@
     </row>
     <row ht="12.75" customHeight="1" r="109">
       <c r="A109" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="110">
+      <c r="A110" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="111">
+      <c r="A111" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="C111" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="D111" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="E109" s="1" t="s">
+      <c r="E111" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="112">
+      <c r="A112" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="E112" s="1" t="s">
         <v>14</v>
       </c>
     </row>

--- a/Empreendimentos.xlsx
+++ b/Empreendimentos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="388">
   <si>
     <t>EMPREENDIMENTO</t>
   </si>
@@ -1106,6 +1106,27 @@
     <t>RD SUMARÉ MONTE MOR KM09 - HARAS LARISSA</t>
   </si>
   <si>
+    <t>2605 - ALESSANDRO ARDUINI</t>
+  </si>
+  <si>
+    <t>33034896883</t>
+  </si>
+  <si>
+    <t>04538083</t>
+  </si>
+  <si>
+    <t>AVENIDA HORÁCIO LAFER, 815 - 8º ANDAR</t>
+  </si>
+  <si>
+    <t>2606 - MARCO FREIRE (FAZENDA BOA VISTA)</t>
+  </si>
+  <si>
+    <t>18540000</t>
+  </si>
+  <si>
+    <t>FAZENDA BOA VISTA, QUADRA VII, LOTE 11</t>
+  </si>
+  <si>
     <t>9991 - DÉBITO ADMINISTRAÇÃO (OBRAS)</t>
   </si>
   <si>
@@ -1128,6 +1149,15 @@
   </si>
   <si>
     <t>RUA PINTASSILGO</t>
+  </si>
+  <si>
+    <t>230801 - CRISTINA FRAGA</t>
+  </si>
+  <si>
+    <t>158.928.017-21</t>
+  </si>
+  <si>
+    <t>RUA PEDROSO ALVARENGA</t>
   </si>
   <si>
     <t>231601 - MARCO FREIRE (ÁREA EXTERNA)</t>
@@ -1432,7 +1462,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E115"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="57.7142857142857" customWidth="1" style="1"/>
@@ -3259,7 +3289,7 @@
         <v>367</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="108">
@@ -3267,47 +3297,47 @@
         <v>368</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>365</v>
+        <v>249</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="109">
       <c r="A109" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>79</v>
+        <v>373</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="110">
       <c r="A110" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="C110" s="1" t="s">
-        <v>250</v>
+        <v>373</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>14</v>
@@ -3315,35 +3345,86 @@
     </row>
     <row ht="12.75" customHeight="1" r="111">
       <c r="A111" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>28</v>
+        <v>377</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>267</v>
+        <v>79</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>268</v>
+        <v>378</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="112">
       <c r="A112" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C112" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="113">
+      <c r="A113" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="114">
+      <c r="A114" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="115">
+      <c r="A115" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C115" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D112" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="E112" s="1" t="s">
+      <c r="D115" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="E115" s="1" t="s">
         <v>14</v>
       </c>
     </row>

--- a/Empreendimentos.xlsx
+++ b/Empreendimentos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="392">
   <si>
     <t>EMPREENDIMENTO</t>
   </si>
@@ -1064,7 +1064,7 @@
     <t xml:space="preserve"> 04351672862</t>
   </si>
   <si>
-    <t>2601 - REGINA CAMPOS SALLES MORAES ABREU</t>
+    <t>2601 - REGINA CAMPOS S. MORAES ABREU</t>
   </si>
   <si>
     <t>04383430856</t>
@@ -1088,7 +1088,7 @@
     <t>RUA BATATAES 586, APT 91</t>
   </si>
   <si>
-    <t>2603 - FERNANDO AUGUSTO COELHO F DE VASCONCELLOS</t>
+    <t>2603 - FERNANDO AUGUSTO VASCONCELLOS</t>
   </si>
   <si>
     <t>22420041</t>
@@ -1125,6 +1125,18 @@
   </si>
   <si>
     <t>FAZENDA BOA VISTA, QUADRA VII, LOTE 11</t>
+  </si>
+  <si>
+    <t>2607 - DAN-DAN EMPREENDIMENTOS (LOJA 02)</t>
+  </si>
+  <si>
+    <t>RUA PEDROSO ALVARENGA, 896</t>
+  </si>
+  <si>
+    <t>2608 - MARIA CAROLINA CARVALHO MONTEIRO DE GOUVEA</t>
+  </si>
+  <si>
+    <t>29335672882</t>
   </si>
   <si>
     <t>9991 - DÉBITO ADMINISTRAÇÃO (OBRAS)</t>
@@ -1462,7 +1474,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E115"/>
+  <dimension ref="A1:E117"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="57.7142857142857" customWidth="1" style="1"/>
@@ -3314,50 +3326,50 @@
         <v>371</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="110">
       <c r="A110" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>373</v>
+        <v>196</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="111">
       <c r="A111" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="C111" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>378</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="112">
@@ -3365,66 +3377,100 @@
         <v>379</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>221</v>
+        <v>377</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="113">
       <c r="A113" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>383</v>
-      </c>
       <c r="E113" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="114">
       <c r="A114" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="C114" s="1" t="s">
-        <v>267</v>
+        <v>221</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>268</v>
+        <v>385</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="115">
       <c r="A115" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>386</v>
+        <v>249</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>387</v>
       </c>
       <c r="E115" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="116">
+      <c r="A116" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="117">
+      <c r="A117" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="E117" s="1" t="s">
         <v>14</v>
       </c>
     </row>

--- a/Empreendimentos.xlsx
+++ b/Empreendimentos.xlsx
@@ -1,18 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/Formulario/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_81148EC54C72739A7BB341269182C3234C53A660" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C64931A-4556-4B52-806B-E5C0505858D5}"/>
+  <bookViews>
+    <workbookView xWindow="28680" yWindow="-3720" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId5"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$1</definedName>
+  </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="401">
   <si>
     <t>EMPREENDIMENTO</t>
   </si>
@@ -632,7 +643,7 @@
     <t>AVENIDA VISCONDE DE ALBUQUERQUE, 29/701</t>
   </si>
   <si>
-    <t xml:space="preserve">2304 -  LEONARDO ALMEIDA BYRRO</t>
+    <t>2304 -  LEONARDO ALMEIDA BYRRO</t>
   </si>
   <si>
     <t>26927536825</t>
@@ -767,7 +778,7 @@
     <t>22630011</t>
   </si>
   <si>
-    <t xml:space="preserve">AVENIDA LÚCIO COSTA, 4260, BLOCO 3 -  AP</t>
+    <t>AVENIDA LÚCIO COSTA, 4260, BLOCO 3 -  AP</t>
   </si>
   <si>
     <t>2317 - LUIZ ALBERTO HESS BORGES</t>
@@ -809,7 +820,7 @@
     <t>01049911</t>
   </si>
   <si>
-    <t xml:space="preserve">RUA FORMOSA, 367 -  ANDAR 15</t>
+    <t>RUA FORMOSA, 367 -  ANDAR 15</t>
   </si>
   <si>
     <t>2404 - LUIZ HENRIQUE FRAGA</t>
@@ -998,7 +1009,7 @@
     <t>AVENIDA VIEIRA SOUTO, 438 - AP 1301</t>
   </si>
   <si>
-    <t>2510 - SAMAUMA EVENTOS LTDA</t>
+    <t>2510 - SAMAUMA EMPREEND. , SERV. E PART. LTDA.</t>
   </si>
   <si>
     <t>26761786000153</t>
@@ -1139,6 +1150,27 @@
     <t>29335672882</t>
   </si>
   <si>
+    <t>2609 - ARNALDO LIBMAN</t>
+  </si>
+  <si>
+    <t>40265765749</t>
+  </si>
+  <si>
+    <t>AVENIDA VIEIRA SOUTO, 610 - AP 601</t>
+  </si>
+  <si>
+    <t>2611 - GUILHERME BOTTURA</t>
+  </si>
+  <si>
+    <t>27842200874</t>
+  </si>
+  <si>
+    <t>04510010</t>
+  </si>
+  <si>
+    <t>PRAÇA PEREIRA COUTINHO, 57 - 10º ANDAR</t>
+  </si>
+  <si>
     <t>9991 - DÉBITO ADMINISTRAÇÃO (OBRAS)</t>
   </si>
   <si>
@@ -1161,6 +1193,12 @@
   </si>
   <si>
     <t>RUA PINTASSILGO</t>
+  </si>
+  <si>
+    <t>222001 - GERSON NASCIMENTO (PÓS OBRA)</t>
+  </si>
+  <si>
+    <t>RUA JORGE COELHO, Nº 147, APTO 141</t>
   </si>
   <si>
     <t>230801 - CRISTINA FRAGA</t>
@@ -1193,14 +1231,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="28"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -1216,38 +1249,42 @@
   </fills>
   <borders count="1">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Larissa-Design">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Larissa">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1285,19 +1322,79 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Larissa">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Larissa">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1470,22 +1567,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:E117"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E120"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.7142857142857" customWidth="1" style="1"/>
-    <col min="2" max="2" width="15" customWidth="1" style="1"/>
-    <col min="3" max="3" width="9" customWidth="1" style="1"/>
-    <col min="4" max="4" width="46.4285714285714" customWidth="1" style="1"/>
-    <col min="5" max="5" width="3.57142857142857" customWidth="1" style="1"/>
-    <col min="6" max="16384" width="11.4285714285714" style="1"/>
+    <col min="1" max="1" width="57.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1" customWidth="1"/>
+    <col min="4" max="4" width="46.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="3.5546875" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row ht="12.75" customHeight="1" r="1">
+    <row r="1" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1502,7 +1596,7 @@
         <v>4</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="2">
+    <row r="2" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1519,7 +1613,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="3">
+    <row r="3" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1536,7 +1630,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="4">
+    <row r="4" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1553,7 +1647,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="5">
+    <row r="5" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
@@ -1570,7 +1664,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="6">
+    <row r="6" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>23</v>
       </c>
@@ -1587,7 +1681,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="7">
+    <row r="7" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
@@ -1604,7 +1698,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="8">
+    <row r="8" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>30</v>
       </c>
@@ -1621,7 +1715,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="9">
+    <row r="9" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>34</v>
       </c>
@@ -1638,7 +1732,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="10">
+    <row r="10" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>37</v>
       </c>
@@ -1655,7 +1749,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="11">
+    <row r="11" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>41</v>
       </c>
@@ -1672,7 +1766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="12">
+    <row r="12" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>45</v>
       </c>
@@ -1689,7 +1783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="13">
+    <row r="13" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>49</v>
       </c>
@@ -1706,7 +1800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="14">
+    <row r="14" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>53</v>
       </c>
@@ -1723,7 +1817,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="15">
+    <row r="15" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>57</v>
       </c>
@@ -1740,7 +1834,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="16">
+    <row r="16" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>61</v>
       </c>
@@ -1757,7 +1851,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="17">
+    <row r="17" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>65</v>
       </c>
@@ -1774,7 +1868,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="18">
+    <row r="18" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>69</v>
       </c>
@@ -1791,7 +1885,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="19">
+    <row r="19" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>72</v>
       </c>
@@ -1808,7 +1902,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="20">
+    <row r="20" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>74</v>
       </c>
@@ -1825,7 +1919,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="21">
+    <row r="21" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>77</v>
       </c>
@@ -1842,471 +1936,471 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="22">
+    <row r="22" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="23">
-      <c r="A23" s="1" t="s">
+      <c r="E23" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="24">
-      <c r="A24" s="1" t="s">
+      <c r="E24" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="25">
-      <c r="A25" s="1" t="s">
+      <c r="E25" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="26">
-      <c r="A26" s="1" t="s">
+      <c r="E26" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="27">
-      <c r="A27" s="1" t="s">
+      <c r="E27" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="28">
-      <c r="A28" s="1" t="s">
+      <c r="E28" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="29">
-      <c r="A29" s="1" t="s">
+      <c r="E29" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="30">
-      <c r="A30" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="31">
-      <c r="A31" s="1" t="s">
+      <c r="E31" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B32" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="32">
-      <c r="A32" s="1" t="s">
+      <c r="E32" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B33" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="33">
-      <c r="A33" s="1" t="s">
+      <c r="E33" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="34">
-      <c r="A34" s="1" t="s">
+      <c r="E34" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B35" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="35">
-      <c r="A35" s="1" t="s">
+      <c r="E35" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B36" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="36">
-      <c r="A36" s="1" t="s">
+      <c r="E36" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="37">
-      <c r="A37" s="1" t="s">
+      <c r="E37" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="38">
-      <c r="A38" s="1" t="s">
+      <c r="E38" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="39">
-      <c r="A39" s="1" t="s">
+      <c r="E39" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B40" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C40" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="40">
-      <c r="A40" s="1" t="s">
+      <c r="E40" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="41">
-      <c r="A41" s="1" t="s">
+      <c r="E41" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B42" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C42" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="42">
-      <c r="A42" s="1" t="s">
+      <c r="E42" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B43" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C43" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D43" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="43">
-      <c r="A43" s="1" t="s">
+      <c r="E43" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B44" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C44" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="44">
-      <c r="A44" s="1" t="s">
+      <c r="E44" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B45" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="45">
-      <c r="A45" s="1" t="s">
+      <c r="E45" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B46" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="46">
-      <c r="A46" s="1" t="s">
+      <c r="E46" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B47" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C47" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="47">
-      <c r="A47" s="1" t="s">
+      <c r="E47" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C48" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="48">
-      <c r="A48" s="1" t="s">
+      <c r="E48" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B49" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="49">
-      <c r="A49" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>167</v>
@@ -2318,1164 +2412,1215 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="50">
+    <row r="50" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B51" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C51" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="51">
-      <c r="A51" s="1" t="s">
+      <c r="E51" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B52" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C52" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="52">
-      <c r="A52" s="1" t="s">
+      <c r="E52" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C53" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="53">
-      <c r="A53" s="1" t="s">
+      <c r="E53" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B54" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C54" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D54" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="54">
-      <c r="A54" s="1" t="s">
+      <c r="E54" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B55" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C55" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E54" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="55">
-      <c r="A55" s="1" t="s">
+      <c r="E55" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B57" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C57" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D57" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="56">
-      <c r="A56" s="1" t="s">
+      <c r="E57" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B58" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C58" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D58" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="57">
-      <c r="A57" s="1" t="s">
+      <c r="E58" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B59" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C59" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D59" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E57" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="58">
-      <c r="A58" s="1" t="s">
+      <c r="E59" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B60" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C60" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D60" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="59">
-      <c r="A59" s="1" t="s">
+      <c r="E60" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B61" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C61" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D61" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="60">
-      <c r="A60" s="1" t="s">
+      <c r="E61" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B62" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C62" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D62" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E60" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="61">
-      <c r="A61" s="1" t="s">
+      <c r="E62" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B63" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C63" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D63" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E61" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="62">
-      <c r="A62" s="1" t="s">
+      <c r="E63" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C64" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="63">
-      <c r="A63" s="1" t="s">
+      <c r="E64" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B65" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C65" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D65" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="E63" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="64">
-      <c r="A64" s="1" t="s">
+      <c r="E65" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B66" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C66" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D66" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="65">
-      <c r="A65" s="1" t="s">
+      <c r="E66" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B68" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C68" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D68" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="66">
-      <c r="A66" s="1" t="s">
+      <c r="E68" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B69" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C69" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D69" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="67">
-      <c r="A67" s="1" t="s">
+      <c r="E69" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B70" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C70" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D70" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="E67" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="68">
-      <c r="A68" s="1" t="s">
+      <c r="E70" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B71" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C71" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D71" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="E68" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="69">
-      <c r="A69" s="1" t="s">
+      <c r="E71" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B72" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C72" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D72" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="E69" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="70">
-      <c r="A70" s="1" t="s">
+      <c r="E72" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B73" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C73" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="D73" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="E70" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="71">
-      <c r="A71" s="1" t="s">
+      <c r="E73" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B74" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C74" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="D74" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="72">
-      <c r="A72" s="1" t="s">
+      <c r="E74" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B75" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C75" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="D75" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="E72" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="73">
-      <c r="A73" s="1" t="s">
+      <c r="E75" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B77" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C77" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="D77" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="E73" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="74">
-      <c r="A74" s="1" t="s">
+      <c r="E77" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C78" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="D78" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="E74" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="75">
-      <c r="A75" s="1" t="s">
+      <c r="E78" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B79" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C79" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="D79" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="76">
-      <c r="A76" s="1" t="s">
+      <c r="E79" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C80" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D80" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="77">
-      <c r="A77" s="1" t="s">
+      <c r="E80" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B81" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C81" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="D81" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="78">
-      <c r="A78" s="1" t="s">
+      <c r="E81" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B83" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C83" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="D83" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E78" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="79">
-      <c r="A79" s="1" t="s">
+      <c r="E83" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B84" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C84" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="D84" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="E79" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="80">
-      <c r="A80" s="1" t="s">
+      <c r="E84" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B85" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C85" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D85" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E80" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="81">
-      <c r="A81" s="1" t="s">
+      <c r="E85" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B86" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C86" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="D86" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="E81" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="82">
-      <c r="A82" s="1" t="s">
+      <c r="E86" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B87" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C87" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="D87" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="E82" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="83">
-      <c r="A83" s="1" t="s">
+      <c r="E87" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B88" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C88" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="D88" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="E83" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="84">
-      <c r="A84" s="1" t="s">
+      <c r="E88" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B89" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C89" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="D89" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="E84" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="85">
-      <c r="A85" s="1" t="s">
+      <c r="E89" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B90" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C90" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="D90" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="E85" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="86">
-      <c r="A86" s="1" t="s">
+      <c r="E90" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B91" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C91" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="D91" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="E86" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="87">
-      <c r="A87" s="1" t="s">
+      <c r="E91" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B92" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C92" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="D92" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="E87" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="88">
-      <c r="A88" s="1" t="s">
+      <c r="E92" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B93" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C93" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="D93" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="E88" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="89">
-      <c r="A89" s="1" t="s">
+      <c r="E93" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B94" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C94" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="D94" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="90">
-      <c r="A90" s="1" t="s">
+      <c r="E94" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B95" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C95" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="D95" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="E90" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="91">
-      <c r="A91" s="1" t="s">
+      <c r="E95" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B96" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C96" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="D96" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="E96" s="1" t="s">
         <v>316</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="92">
-      <c r="A92" s="1" t="s">
+    <row r="97" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B97" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C97" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="D97" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="E92" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="93">
-      <c r="A93" s="1" t="s">
+      <c r="E97" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B98" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C98" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="D93" s="1" t="s">
+      <c r="D98" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="E93" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="94">
-      <c r="A94" s="1" t="s">
+      <c r="E98" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B99" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C99" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="D99" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="E94" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="95">
-      <c r="A95" s="1" t="s">
+      <c r="E99" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B100" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C100" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="D100" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="E95" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="96">
-      <c r="A96" s="1" t="s">
+      <c r="E100" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B101" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C101" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="D101" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="E96" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="97">
-      <c r="A97" s="1" t="s">
+      <c r="E101" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B103" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C103" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="D97" s="1" t="s">
+      <c r="D103" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="E97" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="98">
-      <c r="A98" s="1" t="s">
+      <c r="E103" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B104" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C104" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="D104" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="E98" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="99">
-      <c r="A99" s="1" t="s">
+      <c r="E104" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B105" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C105" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="D105" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="E99" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="100">
-      <c r="A100" s="1" t="s">
+      <c r="E105" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B106" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C106" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="D100" s="1" t="s">
+      <c r="D106" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="E100" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="101">
-      <c r="A101" s="1" t="s">
+      <c r="E106" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B107" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C107" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="D107" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="E101" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="102">
-      <c r="A102" s="1" t="s">
+      <c r="E107" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B108" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="C108" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="D102" s="1" t="s">
+      <c r="D108" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="E102" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="103">
-      <c r="A103" s="1" t="s">
+      <c r="E108" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B109" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C109" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="D103" s="1" t="s">
+      <c r="D109" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="E103" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="104">
-      <c r="A104" s="1" t="s">
+      <c r="E109" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B110" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C110" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="D104" s="1" t="s">
+      <c r="D110" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="E104" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="105">
-      <c r="A105" s="1" t="s">
+      <c r="E110" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B111" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C111" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="D111" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="E105" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="106">
-      <c r="A106" s="1" t="s">
+      <c r="E111" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="B112" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="C112" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D106" s="1" t="s">
+      <c r="D112" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="E106" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="107">
-      <c r="A107" s="1" t="s">
+      <c r="E112" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B113" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C113" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="D107" s="1" t="s">
+      <c r="D113" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="E107" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="108">
-      <c r="A108" s="1" t="s">
+      <c r="E113" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="B114" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C114" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="D108" s="1" t="s">
+      <c r="D114" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="E108" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="109">
-      <c r="A109" s="1" t="s">
+      <c r="E114" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="B115" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="C115" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="D115" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="110">
-      <c r="A110" s="1" t="s">
+      <c r="E115" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B116" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="C116" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="D116" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="E110" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="111">
-      <c r="A111" s="1" t="s">
+      <c r="E116" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="B117" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="C117" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="D111" s="1" t="s">
+      <c r="E117" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="E111" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="112">
-      <c r="A112" s="1" t="s">
+      <c r="B118" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="113">
-      <c r="A113" s="1" t="s">
+      <c r="C118" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="D118" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D113" s="1" t="s">
+      <c r="E118" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="E113" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="114">
-      <c r="A114" s="1" t="s">
+      <c r="B119" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="C119" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="C114" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D114" s="1" t="s">
+      <c r="D119" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="E114" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="115">
-      <c r="A115" s="1" t="s">
+      <c r="E119" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="116">
-      <c r="A116" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="117">
-      <c r="A117" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="E117" s="1" t="s">
+      <c r="B120" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="E120" s="1" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>
-  <pageSetup orientation="portrait" pageOrder="downThenOver" paperSize="9" fitToWidth="0" fitToHeight="0"/>
+  <pageMargins left="0.78740157480314998" right="0.78740157480314998" top="0.78740157480314998" bottom="0.78740157480314998" header="0.39370078740157499" footer="0.39370078740157499"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Empreendimentos.xlsx
+++ b/Empreendimentos.xlsx
@@ -1,29 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/Formulario/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_81148EC54C72739A7BB341269182C3234C53A660" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C64931A-4556-4B52-806B-E5C0505858D5}"/>
-  <bookViews>
-    <workbookView xWindow="28680" yWindow="-3720" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId5"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$1</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="404">
   <si>
     <t>EMPREENDIMENTO</t>
   </si>
@@ -643,7 +632,7 @@
     <t>AVENIDA VISCONDE DE ALBUQUERQUE, 29/701</t>
   </si>
   <si>
-    <t>2304 -  LEONARDO ALMEIDA BYRRO</t>
+    <t xml:space="preserve">2304 -  LEONARDO ALMEIDA BYRRO</t>
   </si>
   <si>
     <t>26927536825</t>
@@ -778,7 +767,7 @@
     <t>22630011</t>
   </si>
   <si>
-    <t>AVENIDA LÚCIO COSTA, 4260, BLOCO 3 -  AP</t>
+    <t xml:space="preserve">AVENIDA LÚCIO COSTA, 4260, BLOCO 3 -  AP</t>
   </si>
   <si>
     <t>2317 - LUIZ ALBERTO HESS BORGES</t>
@@ -820,7 +809,7 @@
     <t>01049911</t>
   </si>
   <si>
-    <t>RUA FORMOSA, 367 -  ANDAR 15</t>
+    <t xml:space="preserve">RUA FORMOSA, 367 -  ANDAR 15</t>
   </si>
   <si>
     <t>2404 - LUIZ HENRIQUE FRAGA</t>
@@ -1169,6 +1158,15 @@
   </si>
   <si>
     <t>PRAÇA PEREIRA COUTINHO, 57 - 10º ANDAR</t>
+  </si>
+  <si>
+    <t>2612 - FABIO DE BARROS PINHEIRO</t>
+  </si>
+  <si>
+    <t>27549720134</t>
+  </si>
+  <si>
+    <t>RUA JOÃO LOURENÇO, 577 - 3º ANDAR</t>
   </si>
   <si>
     <t>9991 - DÉBITO ADMINISTRAÇÃO (OBRAS)</t>
@@ -1231,9 +1229,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="28"/>
+  <fonts count="1">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -1249,42 +1252,38 @@
   </fills>
   <borders count="1">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Larissa-Design">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Larissa">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1322,79 +1321,19 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Larissa">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Larissa">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1567,19 +1506,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E120"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:E121"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="57.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="1" customWidth="1"/>
-    <col min="4" max="4" width="46.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="3.5546875" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="11.44140625" style="1"/>
+    <col min="1" max="1" width="57.7142857142857" customWidth="1" style="1"/>
+    <col min="2" max="2" width="15" customWidth="1" style="1"/>
+    <col min="3" max="3" width="9" customWidth="1" style="1"/>
+    <col min="4" max="4" width="46.4285714285714" customWidth="1" style="1"/>
+    <col min="5" max="5" width="3.57142857142857" customWidth="1" style="1"/>
+    <col min="6" max="16384" width="11.4285714285714" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1596,7 +1538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1613,7 +1555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="3">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1630,7 +1572,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="4">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1647,7 +1589,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="5">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
@@ -1664,7 +1606,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="6">
       <c r="A6" s="1" t="s">
         <v>23</v>
       </c>
@@ -1681,7 +1623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="7">
       <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
@@ -1698,7 +1640,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="8">
       <c r="A8" s="1" t="s">
         <v>30</v>
       </c>
@@ -1715,7 +1657,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="9">
       <c r="A9" s="1" t="s">
         <v>34</v>
       </c>
@@ -1732,7 +1674,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="10">
       <c r="A10" s="1" t="s">
         <v>37</v>
       </c>
@@ -1749,7 +1691,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="11">
       <c r="A11" s="1" t="s">
         <v>41</v>
       </c>
@@ -1766,7 +1708,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="12">
       <c r="A12" s="1" t="s">
         <v>45</v>
       </c>
@@ -1783,7 +1725,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="13">
       <c r="A13" s="1" t="s">
         <v>49</v>
       </c>
@@ -1800,7 +1742,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="14">
       <c r="A14" s="1" t="s">
         <v>53</v>
       </c>
@@ -1817,7 +1759,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="15">
       <c r="A15" s="1" t="s">
         <v>57</v>
       </c>
@@ -1834,7 +1776,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="16">
       <c r="A16" s="1" t="s">
         <v>61</v>
       </c>
@@ -1851,7 +1793,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="17">
       <c r="A17" s="1" t="s">
         <v>65</v>
       </c>
@@ -1868,7 +1810,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="18">
       <c r="A18" s="1" t="s">
         <v>69</v>
       </c>
@@ -1885,7 +1827,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="19">
       <c r="A19" s="1" t="s">
         <v>72</v>
       </c>
@@ -1902,7 +1844,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="20">
       <c r="A20" s="1" t="s">
         <v>74</v>
       </c>
@@ -1919,7 +1861,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="21">
       <c r="A21" s="1" t="s">
         <v>77</v>
       </c>
@@ -1936,471 +1878,471 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="22">
       <c r="A22" s="1" t="s">
-        <v>387</v>
+        <v>81</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>388</v>
+        <v>82</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>389</v>
+        <v>84</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="23">
       <c r="A23" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="24">
       <c r="A24" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="25">
       <c r="A25" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="26">
       <c r="A26" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="27">
+      <c r="A27" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="28">
+      <c r="A28" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="D28" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="29">
       <c r="A29" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>12</v>
+        <v>106</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="30">
       <c r="A30" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="31">
       <c r="A31" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="32">
       <c r="A32" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="33">
+      <c r="A33" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="34">
+      <c r="A34" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="35">
+      <c r="A35" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="36">
+      <c r="A36" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B33" s="1" t="s">
+      <c r="D36" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="37">
+      <c r="A37" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="38">
+      <c r="A38" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="39">
+      <c r="A39" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="40">
+      <c r="A40" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="41">
+      <c r="A41" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="42">
+      <c r="A42" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B34" s="1" t="s">
+      <c r="C42" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="43">
+      <c r="A43" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="44">
+      <c r="A44" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="45">
+      <c r="A45" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="D45" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="46">
       <c r="A46" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>119</v>
+        <v>160</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="47">
       <c r="A47" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>159</v>
+        <v>70</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="48">
       <c r="A48" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="49">
       <c r="A49" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>167</v>
@@ -2412,1215 +2354,1232 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="50">
       <c r="A50" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row ht="12.75" customHeight="1" r="51">
       <c r="A51" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C51" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="52">
+      <c r="A52" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="53">
+      <c r="A53" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="54">
+      <c r="A54" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="55">
+      <c r="A55" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="56">
+      <c r="A56" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="57">
+      <c r="A57" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="58">
+      <c r="A58" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="59">
+      <c r="A59" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="60">
+      <c r="A60" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="61">
+      <c r="A61" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B52" s="1" t="s">
+      <c r="D61" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="62">
+      <c r="A62" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="63">
+      <c r="A63" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="64">
+      <c r="A64" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="65">
+      <c r="A65" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="66">
+      <c r="A66" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="67">
+      <c r="A67" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="68">
+      <c r="A68" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="69">
+      <c r="A69" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="70">
+      <c r="A70" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="71">
+      <c r="A71" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="72">
+      <c r="A72" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="73">
+      <c r="A73" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="74">
+      <c r="A74" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="75">
+      <c r="A75" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="76">
+      <c r="A76" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="77">
+      <c r="A77" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="78">
+      <c r="A78" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="79">
+      <c r="A79" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="80">
+      <c r="A80" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="81">
+      <c r="A81" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="82">
+      <c r="A82" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="83">
+      <c r="A83" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="84">
+      <c r="A84" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="85">
+      <c r="A85" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="86">
+      <c r="A86" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="87">
+      <c r="A87" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="88">
+      <c r="A88" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="89">
+      <c r="A89" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="90">
+      <c r="A90" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="91">
+      <c r="A91" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="92">
+      <c r="A92" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="93">
+      <c r="A93" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="94">
+      <c r="A94" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="95">
+      <c r="A95" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="96">
+      <c r="A96" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="97">
+      <c r="A97" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="98">
+      <c r="A98" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="99">
+      <c r="A99" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="100">
+      <c r="A100" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="101">
+      <c r="A101" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="102">
+      <c r="A102" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="103">
+      <c r="A103" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="104">
+      <c r="A104" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="105">
+      <c r="A105" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="106">
+      <c r="A106" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="107">
+      <c r="A107" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="108">
+      <c r="A108" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="109">
+      <c r="A109" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="110">
+      <c r="A110" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="111">
+      <c r="A111" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="112">
+      <c r="A112" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="113">
+      <c r="A113" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="114">
+      <c r="A114" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="115">
+      <c r="A115" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="116">
+      <c r="A116" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="117">
+      <c r="A117" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C117" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="C66" s="1" t="s">
+      <c r="D117" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="118">
+      <c r="A118" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C118" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="B75" s="1" t="s">
+      <c r="D118" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="119">
+      <c r="A119" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C119" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C81" s="1" t="s">
+      <c r="D119" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="120">
+      <c r="A120" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C120" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="D120" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="E81" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C86" s="1" t="s">
+      <c r="E120" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="121">
+      <c r="A121" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C121" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D86" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="E120" s="1" t="s">
+      <c r="D121" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.78740157480314998" right="0.78740157480314998" top="0.78740157480314998" bottom="0.78740157480314998" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
+  <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>
+  <pageSetup orientation="portrait" pageOrder="downThenOver" paperSize="9" fitToWidth="0" fitToHeight="0"/>
 </worksheet>
 </file>
--- a/Empreendimentos.xlsx
+++ b/Empreendimentos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="406">
   <si>
     <t>EMPREENDIMENTO</t>
   </si>
@@ -1118,7 +1118,7 @@
     <t>AVENIDA HORÁCIO LAFER, 815 - 8º ANDAR</t>
   </si>
   <si>
-    <t>2606 - MARCO FREIRE (FAZENDA BOA VISTA)</t>
+    <t>2606 - MARCO AURÉLIO SIMÃO FREIRE</t>
   </si>
   <si>
     <t>18540000</t>
@@ -1127,13 +1127,13 @@
     <t>FAZENDA BOA VISTA, QUADRA VII, LOTE 11</t>
   </si>
   <si>
-    <t>2607 - DAN-DAN EMPREENDIMENTOS (LOJA 02)</t>
+    <t>2607 - DAN DAN EMPREENDIMENTOS</t>
   </si>
   <si>
     <t>RUA PEDROSO ALVARENGA, 896</t>
   </si>
   <si>
-    <t>2608 - MARIA CAROLINA CARVALHO MONTEIRO DE GOUVEA</t>
+    <t>2608 - MARIA CAROLINA C. M. DE GOUVEA</t>
   </si>
   <si>
     <t>29335672882</t>
@@ -1160,7 +1160,7 @@
     <t>PRAÇA PEREIRA COUTINHO, 57 - 10º ANDAR</t>
   </si>
   <si>
-    <t>2612 - FABIO DE BARROS PINHEIRO</t>
+    <t>2612 - FÁBIO DE BARROS PINHEIRO</t>
   </si>
   <si>
     <t>27549720134</t>
@@ -1169,15 +1169,21 @@
     <t>RUA JOÃO LOURENÇO, 577 - 3º ANDAR</t>
   </si>
   <si>
+    <t>9988 - DÉB. ADM. (DEBITO X CREDITO)</t>
+  </si>
+  <si>
+    <t>72201650000106</t>
+  </si>
+  <si>
+    <t>22270900</t>
+  </si>
+  <si>
+    <t>RUA VOLUNTÁRIOS DA PÁTRIA</t>
+  </si>
+  <si>
     <t>9991 - DÉBITO ADMINISTRAÇÃO (OBRAS)</t>
   </si>
   <si>
-    <t>72201650000106</t>
-  </si>
-  <si>
-    <t>22270900</t>
-  </si>
-  <si>
     <t>RUA VOLUNTÁRIOS DA PATRIA, 45 - 402/403</t>
   </si>
   <si>
@@ -1208,7 +1214,7 @@
     <t>RUA PEDROSO ALVARENGA</t>
   </si>
   <si>
-    <t>231601 - MARCO FREIRE (ÁREA EXTERNA)</t>
+    <t>231601 - MARCO AURÉLIO SIMÃO FREIRE</t>
   </si>
   <si>
     <t>AVENIDA LÚCIO COSTA, 4260, APTO 602/BL03</t>
@@ -1510,7 +1516,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="57.7142857142857" customWidth="1" style="1"/>
@@ -3470,7 +3476,7 @@
         <v>387</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>14</v>
@@ -3478,30 +3484,30 @@
     </row>
     <row ht="12.75" customHeight="1" r="116">
       <c r="A116" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="E116" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="117">
       <c r="A117" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="C117" s="1" t="s">
-        <v>177</v>
+        <v>79</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>394</v>
@@ -3515,13 +3521,13 @@
         <v>395</v>
       </c>
       <c r="B118" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>397</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>9</v>
@@ -3529,19 +3535,19 @@
     </row>
     <row ht="12.75" customHeight="1" r="119">
       <c r="A119" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="C119" s="1" t="s">
-        <v>250</v>
+        <v>221</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>399</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="120">
@@ -3549,13 +3555,13 @@
         <v>400</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>28</v>
+        <v>249</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>268</v>
+        <v>401</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>14</v>
@@ -3563,18 +3569,35 @@
     </row>
     <row ht="12.75" customHeight="1" r="121">
       <c r="A121" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>402</v>
+        <v>28</v>
       </c>
       <c r="C121" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="122">
+      <c r="A122" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C122" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D121" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="E121" s="1" t="s">
+      <c r="D122" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="E122" s="1" t="s">
         <v>14</v>
       </c>
     </row>

--- a/Empreendimentos.xlsx
+++ b/Empreendimentos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="409">
   <si>
     <t>EMPREENDIMENTO</t>
   </si>
@@ -1148,16 +1148,25 @@
     <t>AVENIDA VIEIRA SOUTO, 610 - AP 601</t>
   </si>
   <si>
+    <t>2610 - ASSOCIAÇÃO DE GOVERNANÇA DOS ADQUIRENTES DO ED. URBANO</t>
+  </si>
+  <si>
+    <t>66249009000149</t>
+  </si>
+  <si>
+    <t>RUA URBANO SANTOS, 71</t>
+  </si>
+  <si>
     <t>2611 - GUILHERME BOTTURA</t>
   </si>
   <si>
     <t>27842200874</t>
   </si>
   <si>
-    <t>04510010</t>
-  </si>
-  <si>
-    <t>PRAÇA PEREIRA COUTINHO, 57 - 10º ANDAR</t>
+    <t>04508001</t>
+  </si>
+  <si>
+    <t>RUA LOURENÇO DE ALMEIDA, 568</t>
   </si>
   <si>
     <t>2612 - FÁBIO DE BARROS PINHEIRO</t>
@@ -1516,10 +1525,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="57.7142857142857" customWidth="1" style="1"/>
+    <col min="1" max="1" width="69.1428571428571" customWidth="1" style="1"/>
     <col min="2" max="2" width="15" customWidth="1" style="1"/>
     <col min="3" max="3" width="9" customWidth="1" style="1"/>
     <col min="4" max="4" width="46.4285714285714" customWidth="1" style="1"/>
@@ -3422,24 +3431,24 @@
         <v>379</v>
       </c>
       <c r="C112" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D112" s="1" t="s">
-        <v>381</v>
-      </c>
       <c r="E112" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="113">
       <c r="A113" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="C113" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>243</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>384</v>
@@ -3456,27 +3465,27 @@
         <v>386</v>
       </c>
       <c r="C114" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="D114" s="1" t="s">
-        <v>388</v>
-      </c>
       <c r="E114" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="115">
       <c r="A115" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="C115" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>14</v>
@@ -3484,16 +3493,16 @@
     </row>
     <row ht="12.75" customHeight="1" r="116">
       <c r="A116" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>14</v>
@@ -3501,19 +3510,19 @@
     </row>
     <row ht="12.75" customHeight="1" r="117">
       <c r="A117" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B117" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="118">
@@ -3521,13 +3530,13 @@
         <v>395</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>176</v>
+        <v>396</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>177</v>
+        <v>79</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>9</v>
@@ -3535,13 +3544,13 @@
     </row>
     <row ht="12.75" customHeight="1" r="119">
       <c r="A119" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>398</v>
+        <v>176</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>221</v>
+        <v>177</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>399</v>
@@ -3555,30 +3564,30 @@
         <v>400</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>249</v>
+        <v>401</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>250</v>
+        <v>221</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="121">
       <c r="A121" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>28</v>
+        <v>249</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>268</v>
+        <v>404</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>14</v>
@@ -3586,18 +3595,35 @@
     </row>
     <row ht="12.75" customHeight="1" r="122">
       <c r="A122" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>404</v>
+        <v>28</v>
       </c>
       <c r="C122" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="123">
+      <c r="A123" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C123" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D122" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="E122" s="1" t="s">
+      <c r="D123" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E123" s="1" t="s">
         <v>14</v>
       </c>
     </row>

--- a/Empreendimentos.xlsx
+++ b/Empreendimentos.xlsx
@@ -965,7 +965,7 @@
     <t>SC</t>
   </si>
   <si>
-    <t>2506 - KATIA FERREIRA DE BARROS</t>
+    <t>2506 - KÁTIA FERREIRA DE BARROS</t>
   </si>
   <si>
     <t>22261070</t>
@@ -974,7 +974,7 @@
     <t>RUA EUCLIDES DE FIGUEIREDO, 60</t>
   </si>
   <si>
-    <t>2507 - KATIA FERREIRA DE BARROS</t>
+    <t>2507 - KÁTIA FERREIRA DE BARROS</t>
   </si>
   <si>
     <t>RUA EUCLIDES DE FIGUEIREDO, 76</t>
@@ -1148,7 +1148,7 @@
     <t>AVENIDA VIEIRA SOUTO, 610 - AP 601</t>
   </si>
   <si>
-    <t>2610 - ASSOCIAÇÃO DE GOVERNANÇA DOS ADQUIRENTES DO ED. URBANO</t>
+    <t>2610 - ASSOCIAÇÃO DE GOVERNANÇA DOS A. DO ED. URBANO</t>
   </si>
   <si>
     <t>66249009000149</t>
@@ -1166,7 +1166,7 @@
     <t>04508001</t>
   </si>
   <si>
-    <t>RUA LOURENÇO DE ALMEIDA, 568</t>
+    <t>RUA LOURENÇO DE ALMEIDA, 658</t>
   </si>
   <si>
     <t>2612 - FÁBIO DE BARROS PINHEIRO</t>
@@ -1528,7 +1528,7 @@
   <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="69.1428571428571" customWidth="1" style="1"/>
+    <col min="1" max="1" width="57.8571428571429" customWidth="1" style="1"/>
     <col min="2" max="2" width="15" customWidth="1" style="1"/>
     <col min="3" max="3" width="9" customWidth="1" style="1"/>
     <col min="4" max="4" width="46.4285714285714" customWidth="1" style="1"/>

--- a/Empreendimentos.xlsx
+++ b/Empreendimentos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="413">
   <si>
     <t>EMPREENDIMENTO</t>
   </si>
@@ -998,7 +998,7 @@
     <t>AVENIDA VIEIRA SOUTO, 438 - AP 1301</t>
   </si>
   <si>
-    <t>2510 - SAMAUMA EMPREEND. , SERV. E PART. LTDA.</t>
+    <t>2510 - SAMAUMA EMPREEND. SERV. E PART. LTDA.</t>
   </si>
   <si>
     <t>26761786000153</t>
@@ -1148,7 +1148,7 @@
     <t>AVENIDA VIEIRA SOUTO, 610 - AP 601</t>
   </si>
   <si>
-    <t>2610 - ASSOCIAÇÃO DE GOVERNANÇA DOS A. DO ED. URBANO</t>
+    <t>2610 - A. DE G. DOS A. DO EDIFÍCIO URBANO</t>
   </si>
   <si>
     <t>66249009000149</t>
@@ -1176,6 +1176,18 @@
   </si>
   <si>
     <t>RUA JOÃO LOURENÇO, 577 - 3º ANDAR</t>
+  </si>
+  <si>
+    <t>2613 - ODARA BRASIL LTDA</t>
+  </si>
+  <si>
+    <t>6369819200017</t>
+  </si>
+  <si>
+    <t>22080045</t>
+  </si>
+  <si>
+    <t>RUA FRANCISCO OTAVIANO, 98 - 401</t>
   </si>
   <si>
     <t>9988 - DÉB. ADM. (DEBITO X CREDITO)</t>
@@ -1525,10 +1537,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:E124"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="57.8571428571429" customWidth="1" style="1"/>
+    <col min="1" max="1" width="57.7142857142857" customWidth="1" style="1"/>
     <col min="2" max="2" width="15" customWidth="1" style="1"/>
     <col min="3" max="3" width="9" customWidth="1" style="1"/>
     <col min="4" max="4" width="46.4285714285714" customWidth="1" style="1"/>
@@ -3496,13 +3508,13 @@
         <v>392</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>14</v>
@@ -3510,16 +3522,16 @@
     </row>
     <row ht="12.75" customHeight="1" r="117">
       <c r="A117" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C117" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>390</v>
-      </c>
       <c r="D117" s="1" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>14</v>
@@ -3527,33 +3539,33 @@
     </row>
     <row ht="12.75" customHeight="1" r="118">
       <c r="A118" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>79</v>
+        <v>394</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>397</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="119">
       <c r="A119" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>176</v>
+        <v>400</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>177</v>
+        <v>79</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>9</v>
@@ -3561,16 +3573,16 @@
     </row>
     <row ht="12.75" customHeight="1" r="120">
       <c r="A120" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>401</v>
+        <v>176</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>221</v>
+        <v>177</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>9</v>
@@ -3578,33 +3590,33 @@
     </row>
     <row ht="12.75" customHeight="1" r="121">
       <c r="A121" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>249</v>
+        <v>405</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>250</v>
+        <v>221</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="122">
       <c r="A122" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>28</v>
+        <v>249</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>268</v>
+        <v>408</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>14</v>
@@ -3612,18 +3624,35 @@
     </row>
     <row ht="12.75" customHeight="1" r="123">
       <c r="A123" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>407</v>
+        <v>28</v>
       </c>
       <c r="C123" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="124">
+      <c r="A124" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C124" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D123" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="E123" s="1" t="s">
+      <c r="D124" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E124" s="1" t="s">
         <v>14</v>
       </c>
     </row>
